--- a/storyboards/EP01-v04/EP01-v04-storyboard.xlsx
+++ b/storyboards/EP01-v04/EP01-v04-storyboard.xlsx
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>按新版第三场采用崔赫西装 B 套，并暂按连续行动延续至第四场；B 套尚无用户确认的服装参考图，颜色、内搭与帽子处理均待定妆。第一场仍为原图鸭舌帽、皮夹克 A 套。</t>
+          <t>按用户确认，第三、四场采用崔赫西装 B 套；B 套尚无用户确认的服装参考图，颜色、内搭与帽子处理均待定妆。第一场仍为原图鸭舌帽、皮夹克 A 套。</t>
         </is>
       </c>
     </row>
